--- a/data/all external test set.xlsx
+++ b/data/all external test set.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025年上半年文件\paper3\最终版论文\3.ER（9.30）\返修\代码\二次返修\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025年上半年文件\paper3\最终版论文\3.ER（9.30）\返修\代码\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12174763-1FA6-415B-997A-1416FDC76745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB59F06-97B7-4C31-8D1B-E47D64AB3E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1488" yWindow="300" windowWidth="13092" windowHeight="11796" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="56POPs" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="321">
   <si>
     <t>Smiles</t>
   </si>
@@ -379,9 +379,6 @@
   </si>
   <si>
     <t>C1(=O)N(C(=O)N(C(=O)N1Cl)Cl)Cl</t>
-  </si>
-  <si>
-    <t>smiles</t>
   </si>
   <si>
     <t>smiles</t>
@@ -484,9 +481,6 @@
     <t>CC(C)(C)CC(C)(C)c1ccc(cc1)O</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>OC(=O)C(F)(F)F</t>
   </si>
   <si>
@@ -995,6 +989,10 @@
   </si>
   <si>
     <t>CCCCCCCCCCCCCC=CC</t>
+  </si>
+  <si>
+    <t>labels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2133,7 +2131,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2956,7 +2954,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2970,7 +2968,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2984,7 +2982,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2998,7 +2996,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3012,7 +3010,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3026,7 +3024,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3040,7 +3038,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3054,7 +3052,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3068,7 +3066,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3082,7 +3080,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3096,7 +3094,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3110,7 +3108,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3124,7 +3122,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3138,7 +3136,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3152,7 +3150,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3166,7 +3164,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3180,7 +3178,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3194,7 +3192,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3208,7 +3206,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3222,7 +3220,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3236,7 +3234,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3250,7 +3248,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3264,7 +3262,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -3278,7 +3276,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -3306,7 +3304,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -3320,7 +3318,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3334,7 +3332,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -3348,7 +3346,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -3362,7 +3360,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -3376,7 +3374,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -3390,7 +3388,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -3404,7 +3402,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3424,1902 +3422,1383 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF80F62-AB2E-48AC-8CCB-86B0D5D1552C}">
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:B172"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>150</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>152</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>153</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>154</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>155</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>156</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>157</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>158</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>159</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>160</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>161</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>162</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>163</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>164</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>165</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>166</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>167</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>168</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>169</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>170</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>171</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>172</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>173</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>174</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>175</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>176</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>177</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>178</v>
       </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>179</v>
       </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>180</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>181</v>
       </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>182</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>183</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>184</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>185</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>186</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>187</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>188</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>189</v>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>190</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>191</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>192</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>193</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>194</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>195</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>196</v>
       </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>197</v>
       </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>198</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>199</v>
       </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>200</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>201</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="E52" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>202</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>203</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="E54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>204</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="E55" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>205</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>206</v>
       </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="E57" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>207</v>
       </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>208</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>209</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>210</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>211</v>
       </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>212</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>213</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>214</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>215</v>
       </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>216</v>
       </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>217</v>
       </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>218</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>219</v>
       </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="E70" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>220</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>221</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>222</v>
       </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>223</v>
       </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>224</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>225</v>
       </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="E76" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>226</v>
       </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>227</v>
       </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="E78" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>228</v>
       </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>229</v>
       </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>230</v>
       </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="E81" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>231</v>
       </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="E82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>232</v>
       </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="E83" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>233</v>
       </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="E84" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>234</v>
       </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="E85" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>235</v>
       </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="E86" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>236</v>
       </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>237</v>
       </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>238</v>
       </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="E89" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>239</v>
       </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>240</v>
       </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>241</v>
       </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="E92" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>242</v>
       </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="E93" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>243</v>
       </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="E94" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>244</v>
       </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-      <c r="E95" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>245</v>
       </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-      <c r="E96" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>246</v>
       </c>
-      <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="E97" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>247</v>
       </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="E98" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>248</v>
       </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>249</v>
       </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="E100" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>250</v>
       </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-      <c r="E101" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>251</v>
       </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-      <c r="E102" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>252</v>
       </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-      <c r="E103" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>253</v>
       </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>254</v>
       </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-      <c r="E105" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>255</v>
       </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>256</v>
       </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-      <c r="E107" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>257</v>
       </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="E108" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>258</v>
       </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>259</v>
       </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>260</v>
       </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-      <c r="E111" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>261</v>
       </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-      <c r="E112" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>262</v>
       </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-      <c r="E113" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>263</v>
       </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-      <c r="E114" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>264</v>
       </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-      <c r="E115" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>265</v>
       </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-      <c r="E116" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>266</v>
       </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-      <c r="E117" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>267</v>
       </c>
-      <c r="B118">
-        <v>0</v>
-      </c>
-      <c r="E118" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>268</v>
       </c>
-      <c r="B119">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="B121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>269</v>
       </c>
-      <c r="B120">
-        <v>0</v>
-      </c>
-      <c r="E120" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>270</v>
       </c>
-      <c r="B121">
-        <v>0</v>
-      </c>
-      <c r="E121" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>271</v>
       </c>
-      <c r="B122">
-        <v>0</v>
-      </c>
-      <c r="E122" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>272</v>
       </c>
-      <c r="B123">
-        <v>0</v>
-      </c>
-      <c r="E123" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>273</v>
       </c>
-      <c r="B124">
-        <v>0</v>
-      </c>
-      <c r="E124" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>274</v>
       </c>
-      <c r="B125">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>275</v>
       </c>
-      <c r="B126">
-        <v>0</v>
-      </c>
-      <c r="E126" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>276</v>
       </c>
-      <c r="B127">
-        <v>0</v>
-      </c>
-      <c r="E127" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>277</v>
       </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>278</v>
       </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="E129" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>279</v>
       </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="E130" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>280</v>
       </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="E131" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>281</v>
       </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="E132" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>282</v>
       </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="E133" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>283</v>
       </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>284</v>
       </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="E135" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>285</v>
       </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="E136" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>286</v>
       </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="E137" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>287</v>
       </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="E138" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>288</v>
       </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-      <c r="E139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>289</v>
       </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="E140" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>290</v>
       </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>291</v>
       </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>292</v>
       </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>293</v>
       </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="E144" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>294</v>
       </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>295</v>
       </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>296</v>
       </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>297</v>
       </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>298</v>
       </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>299</v>
       </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>300</v>
       </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="E151" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>301</v>
       </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="E152" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>302</v>
       </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="E153" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>303</v>
       </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="E154" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>304</v>
       </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="E155" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>305</v>
       </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="E156" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>306</v>
       </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-      <c r="E157" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>307</v>
       </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-      <c r="E158" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>308</v>
       </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-      <c r="E159" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>309</v>
       </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-      <c r="E160" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>310</v>
       </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-      <c r="E161" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>311</v>
       </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="E162" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>312</v>
       </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="E163" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>313</v>
       </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="E164" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>314</v>
       </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-      <c r="E165" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>315</v>
       </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-      <c r="E166" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>316</v>
       </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-      <c r="E167" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>317</v>
       </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-      <c r="E168" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>318</v>
       </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-      <c r="E169" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>319</v>
       </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-      <c r="E170" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>320</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-      <c r="E171" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>321</v>
-      </c>
       <c r="B172">
         <v>0</v>
-      </c>
-      <c r="E172" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
